--- a/docs/downloads/11/tbl_cultures_touchees_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_marovoay_tous.xlsx
@@ -693,12 +693,6 @@
           <t>mais</t>
         </is>
       </c>
-      <c r="C19">
-        <v>4</v>
-      </c>
-      <c r="D19">
-        <v>9.1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -711,12 +705,6 @@
           <t>Black Eyes</t>
         </is>
       </c>
-      <c r="C20">
-        <v>4</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -729,12 +717,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C21">
-        <v>4</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -747,12 +729,6 @@
           <t>cane à sucre</t>
         </is>
       </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22">
-        <v>3.6</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -765,12 +741,6 @@
           <t>Concombre</t>
         </is>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -783,12 +753,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -801,12 +765,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -819,12 +777,6 @@
           <t>Concombre</t>
         </is>
       </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -837,12 +789,6 @@
           <t>Black Eyes</t>
         </is>
       </c>
-      <c r="C27">
-        <v>2</v>
-      </c>
-      <c r="D27">
-        <v>2.4</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -855,12 +801,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C28">
-        <v>2</v>
-      </c>
-      <c r="D28">
-        <v>4.5</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -873,12 +813,6 @@
           <t>patate douce</t>
         </is>
       </c>
-      <c r="C29">
-        <v>2</v>
-      </c>
-      <c r="D29">
-        <v>4.5</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -891,12 +825,6 @@
           <t>Black Eyes</t>
         </is>
       </c>
-      <c r="C30">
-        <v>2</v>
-      </c>
-      <c r="D30">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -909,12 +837,6 @@
           <t>cane à sucre</t>
         </is>
       </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -927,12 +849,6 @@
           <t>manioc</t>
         </is>
       </c>
-      <c r="C32">
-        <v>2</v>
-      </c>
-      <c r="D32">
-        <v>1.9</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -945,12 +861,6 @@
           <t>Banane</t>
         </is>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-      <c r="D33">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -963,12 +873,6 @@
           <t>Brède</t>
         </is>
       </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -981,12 +885,6 @@
           <t>arachide</t>
         </is>
       </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>1.2</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -999,12 +897,6 @@
           <t>Aubergine</t>
         </is>
       </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1017,12 +909,6 @@
           <t>Autres légumes</t>
         </is>
       </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-      <c r="D37">
-        <v>2.3</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1035,12 +921,6 @@
           <t>Voanemba</t>
         </is>
       </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-      <c r="D38">
-        <v>0.7</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1053,12 +933,6 @@
           <t>Aubergine</t>
         </is>
       </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1071,12 +945,6 @@
           <t>Courge</t>
         </is>
       </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1089,12 +957,6 @@
           <t>Pomme de terre</t>
         </is>
       </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1106,12 +968,6 @@
         <is>
           <t>arachide</t>
         </is>
-      </c>
-      <c r="C42">
-        <v>1</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/11/tbl_cultures_touchees_marovoay_tous.xlsx
+++ b/docs/downloads/11/tbl_cultures_touchees_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -397,7 +397,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -415,7 +415,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -451,7 +451,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -469,7 +469,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -487,7 +487,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -505,7 +505,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -523,7 +523,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -559,7 +559,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -613,7 +613,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -649,7 +649,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -685,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -697,7 +697,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -709,7 +709,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -757,7 +757,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -769,7 +769,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -793,7 +793,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -817,7 +817,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -937,7 +937,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -949,7 +949,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
